--- a/documentacion/entregables/Normalizacion_Modelo_Relacional_MetaFit.xlsx
+++ b/documentacion/entregables/Normalizacion_Modelo_Relacional_MetaFit.xlsx
@@ -3255,7 +3255,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>MAPA: RELACIÓN NORMALIZADA (3FN) -&gt; TABLA FÍSICA EN MYSQL/MARIADB</t>
+          <t>MAPA: RELACIÓN NORMALIZADA (3FN) -&gt; TABLA FÍSICA EN MARIADB 11</t>
         </is>
       </c>
     </row>
